--- a/Batch_Validation_Output.xlsx
+++ b/Batch_Validation_Output.xlsx
@@ -10,7 +10,6 @@
     <sheet name="21" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="22" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="23" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Combined_Average" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,315 +438,349 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Roll</t>
+          <t>Expected_Yaw</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Mean</t>
+          <t>Yaw_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Roll_MAE</t>
+          <t>Yaw_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Roll_RMSE</t>
+          <t>Yaw_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Bias</t>
+          <t>Yaw_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Roll_STD</t>
+          <t>Yaw_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Lower_LOA</t>
+          <t>Yaw_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Upper_LOA</t>
+          <t>Yaw_Upper_LOA</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Roll30.xlsx</t>
+          <t>Yaw0.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>33.274</v>
+        <v>-0.495</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>3.274</v>
+        <v>0.495</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>3.303</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3.274</v>
+        <v>-0.495</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.433</v>
+        <v>0.637</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.425</v>
+        <v>-1.744</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4.123</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roll45.xlsx</t>
+          <t>Yaw30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>47.24</v>
+        <v>27.181</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.24</v>
+        <v>2.819</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>2.255</v>
+        <v>2.819</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2.24</v>
+        <v>-2.819</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.261</v>
+        <v>0.033</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.728</v>
+        <v>-2.883</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2.751</v>
+        <v>-2.754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roll60.xlsx</t>
+          <t>Yaw45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>61.548</v>
+        <v>44.907</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.548</v>
+        <v>0.093</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1.548</v>
+        <v>0.103</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.548</v>
+        <v>-0.093</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.472</v>
+        <v>-0.179</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.624</v>
+        <v>-0.007</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roll90.xlsx</t>
+          <t>Yaw60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93.045</v>
+        <v>55.661</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>3.045</v>
+        <v>4.339</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3.057</v>
+        <v>4.339</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>3.045</v>
+        <v>-4.339</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.269</v>
+        <v>0.035</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2.518</v>
+        <v>-4.407</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3.572</v>
+        <v>-4.271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Roll-30.xlsx</t>
+          <t>Yaw90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-30</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-31.148</v>
+        <v>84.90900000000001</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.148</v>
+        <v>5.091</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.152</v>
+        <v>5.091</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-1.148</v>
+        <v>-5.091</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.093</v>
+        <v>0.023</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-1.33</v>
+        <v>-5.136</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-0.966</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Roll-45.xlsx</t>
+          <t>Yaw-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-45.683</v>
+        <v>-27.091</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.909</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.6840000000000001</v>
+        <v>2.91</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-0.6830000000000001</v>
+        <v>2.909</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.754</v>
+        <v>2.813</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-0.611</v>
+        <v>3.006</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roll-60.xlsx</t>
+          <t>Yaw-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-65.205</v>
+        <v>-43.049</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>5.205</v>
+        <v>1.951</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>5.206</v>
+        <v>1.954</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-5.205</v>
+        <v>1.951</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.079</v>
+        <v>0.094</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-5.361</v>
+        <v>1.768</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-5.05</v>
+        <v>2.135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Roll-90.xlsx</t>
+          <t>Yaw-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>-60</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>-56.967</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>2.963</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>3.104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yaw-90.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>145</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>-91.072</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1.072</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>-1.072</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>-1.322</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>-0.822</v>
+      <c r="D10" s="1" t="n">
+        <v>-92.616</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>-2.616</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>-2.783</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>-2.45</v>
       </c>
     </row>
   </sheetData>
@@ -761,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,315 +810,349 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Roll</t>
+          <t>Expected_Yaw</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Mean</t>
+          <t>Yaw_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Roll_MAE</t>
+          <t>Yaw_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Roll_RMSE</t>
+          <t>Yaw_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Bias</t>
+          <t>Yaw_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Roll_STD</t>
+          <t>Yaw_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Lower_LOA</t>
+          <t>Yaw_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Upper_LOA</t>
+          <t>Yaw_Upper_LOA</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Roll30.xlsx</t>
+          <t>Yaw0.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>35.684</v>
+        <v>-0.468</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>5.684</v>
+        <v>0.468</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>5.731</v>
+        <v>0.469</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>5.684</v>
+        <v>-0.468</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.737</v>
+        <v>0.016</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4.24</v>
+        <v>-0.5</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>7.127</v>
+        <v>-0.437</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roll45.xlsx</t>
+          <t>Yaw30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>49.887</v>
+        <v>29.059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>4.887</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>4.93</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>4.887</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.648</v>
+        <v>0.05</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.618</v>
+        <v>-1.04</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>6.157</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roll60.xlsx</t>
+          <t>Yaw45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>63.416</v>
+        <v>41.553</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3.416</v>
+        <v>3.447</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3.417</v>
+        <v>3.448</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>3.416</v>
+        <v>-3.447</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.081</v>
+        <v>0.043</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>3.258</v>
+        <v>-3.533</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>3.574</v>
+        <v>-3.362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roll90.xlsx</t>
+          <t>Yaw60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>92.38800000000001</v>
+        <v>57.434</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.388</v>
+        <v>2.566</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2.434</v>
+        <v>2.567</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2.388</v>
+        <v>-2.566</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.473</v>
+        <v>0.042</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.462</v>
+        <v>-2.648</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3.314</v>
+        <v>-2.485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Roll-30.xlsx</t>
+          <t>Yaw90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-30</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-31.886</v>
+        <v>85.026</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.886</v>
+        <v>4.974</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.888</v>
+        <v>4.975</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-1.886</v>
+        <v>-4.974</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.076</v>
+        <v>0.032</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-2.035</v>
+        <v>-5.037</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-1.737</v>
+        <v>-4.912</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Roll-45.xlsx</t>
+          <t>Yaw-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-46.945</v>
+        <v>-30.241</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.945</v>
+        <v>0.241</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1.946</v>
+        <v>0.245</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-1.945</v>
+        <v>-0.241</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-2.029</v>
+        <v>-0.321</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-1.861</v>
+        <v>-0.161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roll-60.xlsx</t>
+          <t>Yaw-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-69.919</v>
+        <v>-42.73</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>9.919</v>
+        <v>2.27</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>9.919</v>
+        <v>2.271</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-9.919</v>
+        <v>2.27</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.098</v>
+        <v>0.057</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-10.111</v>
+        <v>2.158</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-9.726000000000001</v>
+        <v>2.383</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Roll-90.xlsx</t>
+          <t>Yaw-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>-60</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>-57.654</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>2.348</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>2.526</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yaw-90.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>145</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>-92.51000000000001</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2.511</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>-2.349</v>
+      <c r="D10" s="1" t="n">
+        <v>-92.449</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>-2.449</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>-2.587</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>-2.312</v>
       </c>
     </row>
   </sheetData>
@@ -1099,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,653 +1182,349 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Roll</t>
+          <t>Expected_Yaw</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Mean</t>
+          <t>Yaw_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Roll_MAE</t>
+          <t>Yaw_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Roll_RMSE</t>
+          <t>Yaw_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Bias</t>
+          <t>Yaw_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Roll_STD</t>
+          <t>Yaw_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Lower_LOA</t>
+          <t>Yaw_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Roll_Upper_LOA</t>
+          <t>Yaw_Upper_LOA</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Roll30.xlsx</t>
+          <t>Yaw0.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>30.709</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.709</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.719</v>
+        <v>0.819</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.709</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.122</v>
+        <v>0.03</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.47</v>
+        <v>-0.878</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0.948</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roll45.xlsx</t>
+          <t>Yaw30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46.513</v>
+        <v>26.504</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.513</v>
+        <v>3.496</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.523</v>
+        <v>3.496</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.513</v>
+        <v>-3.496</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.18</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.161</v>
+        <v>-3.631</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1.865</v>
+        <v>-3.361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roll60.xlsx</t>
+          <t>Yaw45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>62.035</v>
+        <v>41.824</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>2.035</v>
+        <v>3.176</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2.035</v>
+        <v>3.176</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>2.035</v>
+        <v>-3.176</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.014</v>
+        <v>0.053</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2.008</v>
+        <v>-3.279</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2.062</v>
+        <v>-3.073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roll90.xlsx</t>
+          <t>Yaw60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>92.976</v>
+        <v>58.504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.976</v>
+        <v>1.496</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2.977</v>
+        <v>1.497</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2.976</v>
+        <v>-1.496</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2.811</v>
+        <v>-1.607</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3.141</v>
+        <v>-1.386</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Roll-30.xlsx</t>
+          <t>Yaw90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-30</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-30.843</v>
+        <v>88.014</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.843</v>
+        <v>1.986</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.844</v>
+        <v>1.986</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.843</v>
+        <v>-1.986</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.031</v>
+        <v>0.014</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-0.905</v>
+        <v>-2.014</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-0.782</v>
+        <v>-1.958</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Roll-45.xlsx</t>
+          <t>Yaw-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-45.904</v>
+        <v>-34.869</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.904</v>
+        <v>4.869</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.904</v>
+        <v>4.869</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-0.904</v>
+        <v>-4.869</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-4.932</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-0.865</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roll-60.xlsx</t>
+          <t>Yaw-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-62.139</v>
+        <v>-46.279</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.139</v>
+        <v>1.279</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>2.139</v>
+        <v>1.282</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-2.139</v>
+        <v>-1.279</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-2.183</v>
+        <v>-1.45</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-2.095</v>
+        <v>-1.108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Roll-90.xlsx</t>
+          <t>Yaw-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>-60</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>-61.823</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>-1.823</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>-1.917</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>-1.728</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yaw-90.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>145</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>-92.991</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>2.991</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2.991</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>-2.991</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>-3.059</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>-2.923</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>File_Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Sample_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Expected_Roll</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_Mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_MAE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_RMSE</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_Bias</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_STD</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_Lower_LOA</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Roll_Upper_LOA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Roll30.xlsx</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>426</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>33.222</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>3.222</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>3.842</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>3.222</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>2.092</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>-0.877</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>7.322</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Roll45.xlsx</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>414</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>47.88</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>3.251</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>1.509</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>-0.077</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>5.837</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Roll60.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>417</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>62.333</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2.464</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>3.888</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Roll90.xlsx</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>435</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>92.803</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>2.803</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>2.836</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>2.803</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>1.954</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>3.652</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Roll-30.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>441</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>-30</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>-31.292</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1.292</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>-1.292</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>-2.162</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>-0.423</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Roll-45.xlsx</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>447</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>-45</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>-46.177</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>1.177</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>-1.177</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>-2.258</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>-0.096</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Roll-60.xlsx</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>444</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>-60</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>-65.754</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>5.754</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>6.585</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>-5.754</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>3.201</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>-12.028</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.519</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Roll-90.xlsx</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>423</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>-90</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>-92.191</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>2.191</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2.339</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>-2.191</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>-3.798</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>-0.583</v>
+      <c r="D10" s="1" t="n">
+        <v>-89.012</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1.096</v>
       </c>
     </row>
   </sheetData>

--- a/Batch_Validation_Output.xlsx
+++ b/Batch_Validation_Output.xlsx
@@ -438,42 +438,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Yaw</t>
+          <t>Expected_Pitch</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Mean</t>
+          <t>Pitch_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_MAE</t>
+          <t>Pitch_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_RMSE</t>
+          <t>Pitch_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Bias</t>
+          <t>Pitch_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_STD</t>
+          <t>Pitch_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Lower_LOA</t>
+          <t>Pitch_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Upper_LOA</t>
+          <t>Pitch_Upper_LOA</t>
         </is>
       </c>
     </row>
@@ -490,297 +490,297 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>-0.495</v>
+        <v>-0.002</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.495</v>
+        <v>0.014</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>-0.495</v>
+        <v>-0.002</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.637</v>
+        <v>0.017</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-1.744</v>
+        <v>-0.035</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0.755</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yaw30.xlsx</t>
+          <t>Pitch30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>27.181</v>
+        <v>28.694</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.819</v>
+        <v>1.306</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>2.819</v>
+        <v>1.313</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>-2.819</v>
+        <v>-1.306</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.033</v>
+        <v>0.135</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-2.883</v>
+        <v>-1.57</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-2.754</v>
+        <v>-1.043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yaw45.xlsx</t>
+          <t>Pitch45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44.907</v>
+        <v>44.252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.093</v>
+        <v>0.748</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.103</v>
+        <v>0.756</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>-0.093</v>
+        <v>-0.748</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.044</v>
+        <v>0.111</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-0.179</v>
+        <v>-0.965</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yaw60.xlsx</t>
+          <t>Pitch60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>55.661</v>
+        <v>57.911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>4.339</v>
+        <v>2.089</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>4.339</v>
+        <v>2.095</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-4.339</v>
+        <v>-2.089</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.035</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-4.407</v>
+        <v>-2.383</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-4.271</v>
+        <v>-1.795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yaw90.xlsx</t>
+          <t>Pitch90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>84.90900000000001</v>
+        <v>88.19</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>5.091</v>
+        <v>1.81</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>5.091</v>
+        <v>1.811</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-5.091</v>
+        <v>-1.81</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.023</v>
+        <v>0.078</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-5.136</v>
+        <v>-1.963</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-5.046</v>
+        <v>-1.656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yaw-30.xlsx</t>
+          <t>Pitch-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-27.091</v>
+        <v>-28.382</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.909</v>
+        <v>1.618</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>2.91</v>
+        <v>1.618</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>2.909</v>
+        <v>1.618</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.049</v>
+        <v>0.027</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.813</v>
+        <v>1.566</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3.006</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yaw-45.xlsx</t>
+          <t>Pitch-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-43.049</v>
+        <v>-42.306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.951</v>
+        <v>2.694</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>1.954</v>
+        <v>2.695</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.951</v>
+        <v>2.694</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>1.768</v>
+        <v>2.531</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>2.135</v>
+        <v>2.857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yaw-60.xlsx</t>
+          <t>Pitch-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-60</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>-56.967</v>
+        <v>-59.144</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>3.033</v>
+        <v>0.856</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>3.033</v>
+        <v>0.857</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>3.033</v>
+        <v>0.856</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>2.963</v>
+        <v>0.796</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>3.104</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yaw-90.xlsx</t>
+          <t>Pitch-90.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>-92.616</v>
+        <v>-84.846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.616</v>
+        <v>5.154</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2.618</v>
+        <v>5.155</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-2.616</v>
+        <v>5.154</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-2.783</v>
+        <v>4.965</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-2.45</v>
+        <v>5.343</v>
       </c>
     </row>
   </sheetData>
@@ -810,42 +810,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Yaw</t>
+          <t>Expected_Pitch</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Mean</t>
+          <t>Pitch_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_MAE</t>
+          <t>Pitch_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_RMSE</t>
+          <t>Pitch_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Bias</t>
+          <t>Pitch_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_STD</t>
+          <t>Pitch_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Lower_LOA</t>
+          <t>Pitch_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Upper_LOA</t>
+          <t>Pitch_Upper_LOA</t>
         </is>
       </c>
     </row>
@@ -862,297 +862,297 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>-0.468</v>
+        <v>-0.016</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.468</v>
+        <v>0.017</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.469</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>-0.468</v>
+        <v>-0.016</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.5</v>
+        <v>-0.04</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.437</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yaw30.xlsx</t>
+          <t>Pitch30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>29.059</v>
+        <v>28.733</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.267</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-1.267</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-1.04</v>
+        <v>-1.425</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-0.843</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yaw45.xlsx</t>
+          <t>Pitch45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>41.553</v>
+        <v>44.265</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3.447</v>
+        <v>0.735</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3.448</v>
+        <v>0.735</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>-3.447</v>
+        <v>-0.735</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-3.533</v>
+        <v>-0.775</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-3.362</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yaw60.xlsx</t>
+          <t>Pitch60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>57.434</v>
+        <v>57.746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.566</v>
+        <v>2.254</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2.567</v>
+        <v>2.254</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-2.566</v>
+        <v>-2.254</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0.042</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-2.648</v>
+        <v>-2.337</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-2.485</v>
+        <v>-2.171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yaw90.xlsx</t>
+          <t>Pitch90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>85.026</v>
+        <v>90.279</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>4.974</v>
+        <v>0.279</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4.975</v>
+        <v>0.279</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-4.974</v>
+        <v>0.279</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-5.037</v>
+        <v>0.252</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.912</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yaw-30.xlsx</t>
+          <t>Pitch-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-30.241</v>
+        <v>-28.511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.241</v>
+        <v>1.489</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.245</v>
+        <v>1.491</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-0.241</v>
+        <v>1.489</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.041</v>
+        <v>0.075</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.321</v>
+        <v>1.342</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-0.161</v>
+        <v>1.636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yaw-45.xlsx</t>
+          <t>Pitch-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-42.73</v>
+        <v>-41.67</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.27</v>
+        <v>3.33</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>2.271</v>
+        <v>3.331</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>2.27</v>
+        <v>3.33</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.057</v>
+        <v>0.044</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2.158</v>
+        <v>3.244</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>2.383</v>
+        <v>3.417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yaw-60.xlsx</t>
+          <t>Pitch-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-60</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>-57.654</v>
+        <v>-60.247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.346</v>
+        <v>0.247</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2.348</v>
+        <v>0.251</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>2.346</v>
+        <v>-0.247</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.092</v>
+        <v>0.04</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>2.165</v>
+        <v>-0.326</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>2.526</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yaw-90.xlsx</t>
+          <t>Pitch-90.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>-92.449</v>
+        <v>-86.795</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.449</v>
+        <v>3.205</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2.45</v>
+        <v>3.205</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-2.449</v>
+        <v>3.205</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-2.587</v>
+        <v>3.172</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-2.312</v>
+        <v>3.238</v>
       </c>
     </row>
   </sheetData>
@@ -1182,42 +1182,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected_Yaw</t>
+          <t>Expected_Pitch</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Mean</t>
+          <t>Pitch_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_MAE</t>
+          <t>Pitch_MAE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_RMSE</t>
+          <t>Pitch_RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Bias</t>
+          <t>Pitch_Bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_STD</t>
+          <t>Pitch_STD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Lower_LOA</t>
+          <t>Pitch_Lower_LOA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Yaw_Upper_LOA</t>
+          <t>Pitch_Upper_LOA</t>
         </is>
       </c>
     </row>
@@ -1234,297 +1234,297 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>-0.8179999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.819</v>
+        <v>0.024</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>-0.8179999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.878</v>
+        <v>-0.03</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.759</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yaw30.xlsx</t>
+          <t>Pitch30.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>26.504</v>
+        <v>28.922</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>3.496</v>
+        <v>1.078</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>3.496</v>
+        <v>1.078</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>-3.496</v>
+        <v>-1.078</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-3.631</v>
+        <v>-1.104</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-3.361</v>
+        <v>-1.053</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yaw45.xlsx</t>
+          <t>Pitch45.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>41.824</v>
+        <v>45.27</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3.176</v>
+        <v>0.27</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3.176</v>
+        <v>0.287</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>-3.176</v>
+        <v>0.27</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.053</v>
+        <v>0.097</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-3.279</v>
+        <v>0.079</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-3.073</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yaw60.xlsx</t>
+          <t>Pitch60.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>58.504</v>
+        <v>58.254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.496</v>
+        <v>1.746</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1.497</v>
+        <v>1.747</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-1.496</v>
+        <v>-1.746</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.056</v>
+        <v>0.064</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-1.607</v>
+        <v>-1.872</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-1.386</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yaw90.xlsx</t>
+          <t>Pitch90.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>90</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>88.014</v>
+        <v>89.381</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.986</v>
+        <v>0.619</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.986</v>
+        <v>0.619</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-1.986</v>
+        <v>-0.619</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-2.014</v>
+        <v>-0.649</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-1.958</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yaw-30.xlsx</t>
+          <t>Pitch-30.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-30</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-34.869</v>
+        <v>-28.191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4.869</v>
+        <v>1.809</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>4.869</v>
+        <v>1.809</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-4.869</v>
+        <v>1.809</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-4.932</v>
+        <v>1.779</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-4.806</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yaw-45.xlsx</t>
+          <t>Pitch-45.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-46.279</v>
+        <v>-43.753</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.279</v>
+        <v>1.247</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>1.282</v>
+        <v>1.249</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-1.279</v>
+        <v>1.247</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-1.45</v>
+        <v>1.116</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-1.108</v>
+        <v>1.379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yaw-60.xlsx</t>
+          <t>Pitch-60.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-60</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>-61.823</v>
+        <v>-58.508</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.823</v>
+        <v>1.492</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>1.823</v>
+        <v>1.493</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-1.823</v>
+        <v>1.492</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.048</v>
+        <v>0.036</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-1.917</v>
+        <v>1.421</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-1.728</v>
+        <v>1.563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yaw-90.xlsx</t>
+          <t>Pitch-90.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-90</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>-89.012</v>
+        <v>-85.318</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.988</v>
+        <v>4.682</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.989</v>
+        <v>4.682</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.988</v>
+        <v>4.682</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.055</v>
+        <v>0.017</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.88</v>
+        <v>4.65</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1.096</v>
+        <v>4.714</v>
       </c>
     </row>
   </sheetData>
